--- a/results/config/overall_summary.xlsx
+++ b/results/config/overall_summary.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W38"/>
+  <dimension ref="A1:W39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.005" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -629,46 +629,46 @@
         <v>0.05</v>
       </c>
       <c r="J2" t="n">
-        <v>26.2</v>
+        <v>23.46666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>6.405794446242586</v>
+        <v>6.002682234694538</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R2" t="n">
         <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9480094038940957</v>
+        <v>0.9534337625043391</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1824321416020393</v>
+        <v>0.1821629745264848</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1820329342782497</v>
+        <v>0.1817820128053427</v>
       </c>
       <c r="V2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="W2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -2676,7 +2676,7 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kjsd__advperagentrankweighted__M4__L8__eps0p03__g0p0005__ds0p05__dm0p05</t>
+          <t>kjsd__advperagentrankweighted__M4__L24__eps0p02__g0p0005__ds0p2__dm0p05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2693,40 +2693,40 @@
         <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G29" t="n">
         <v>0.0005</v>
       </c>
       <c r="H29" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="I29" t="n">
         <v>0.05</v>
       </c>
       <c r="J29" t="n">
-        <v>98.33333333333333</v>
+        <v>91.2</v>
       </c>
       <c r="K29" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="L29" t="n">
-        <v>12.68102904648764</v>
+        <v>4.601121600201822</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2735,25 +2735,25 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.8048740625032873</v>
+        <v>0.819047619047619</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2361221594115098</v>
+        <v>0.2040829122066498</v>
       </c>
       <c r="U29" t="n">
-        <v>0.2360454335808754</v>
+        <v>0.2034393876791</v>
       </c>
       <c r="V29" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="W29" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kjsd__advperagentrankweighted__M4__L8__eps0p03__g0p0005__ds0p2__dm0p05</t>
+          <t>kjsd__advperagentrankweighted__M4__L8__eps0p03__g0p0005__ds0p05__dm0p05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2779,19 +2779,19 @@
         <v>0.0005</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="I30" t="n">
         <v>0.05</v>
       </c>
       <c r="J30" t="n">
-        <v>99.86666666666666</v>
+        <v>98.33333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>93.5</v>
+        <v>95</v>
       </c>
       <c r="L30" t="n">
-        <v>11.86839975553116</v>
+        <v>12.68102904648764</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.8018321289196041</v>
+        <v>0.8048740625032873</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2360576925178369</v>
+        <v>0.2361221594115098</v>
       </c>
       <c r="U30" t="n">
-        <v>0.235967646787564</v>
+        <v>0.2360454335808754</v>
       </c>
       <c r="V30" t="n">
         <v>30</v>
@@ -2830,7 +2830,7 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kjsd__advperagentrankweighted__M4__L8__eps0p02__g0p0003__ds0p2__dm0p05</t>
+          <t>kjsd__advperagentrankweighted__M4__L8__eps0p03__g0p0005__ds0p2__dm0p05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2850,10 +2850,10 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0003</v>
+        <v>0.0005</v>
       </c>
       <c r="H31" t="n">
         <v>0.2</v>
@@ -2862,22 +2862,22 @@
         <v>0.05</v>
       </c>
       <c r="J31" t="n">
-        <v>105.0666666666667</v>
+        <v>99.86666666666666</v>
       </c>
       <c r="K31" t="n">
-        <v>94.5</v>
+        <v>93.5</v>
       </c>
       <c r="L31" t="n">
-        <v>12.89123209195435</v>
+        <v>11.86839975553116</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
         <v>3</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.7915154575194338</v>
+        <v>0.8018321289196041</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2399612617989381</v>
+        <v>0.2360576925178369</v>
       </c>
       <c r="U31" t="n">
-        <v>0.2398798334101836</v>
+        <v>0.235967646787564</v>
       </c>
       <c r="V31" t="n">
         <v>30</v>
@@ -2907,7 +2907,7 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kjsd__advperagentrankweighted__M4__L8__eps0p02__g0p0003__ds0p05__dm0p05</t>
+          <t>kjsd__advperagentrankweighted__M4__L8__eps0p02__g0p0003__ds0p2__dm0p05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2933,19 +2933,19 @@
         <v>0.0003</v>
       </c>
       <c r="H32" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="I32" t="n">
         <v>0.05</v>
       </c>
       <c r="J32" t="n">
-        <v>107.4</v>
+        <v>105.0666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>99</v>
+        <v>94.5</v>
       </c>
       <c r="L32" t="n">
-        <v>12.81719609944432</v>
+        <v>12.89123209195435</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2966,13 +2966,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.7868845130276544</v>
+        <v>0.7915154575194338</v>
       </c>
       <c r="T32" t="n">
-        <v>0.23768160790205</v>
+        <v>0.2399612617989381</v>
       </c>
       <c r="U32" t="n">
-        <v>0.2376122422516346</v>
+        <v>0.2398798334101836</v>
       </c>
       <c r="V32" t="n">
         <v>30</v>
@@ -2984,7 +2984,7 @@
     <row r="33" ht="18" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kjsd__advperagentrankweighted__M4__L12__eps0p03__g0p0003__ds0p2__dm0p05</t>
+          <t>kjsd__advperagentrankweighted__M4__L8__eps0p02__g0p0003__ds0p05__dm0p05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3001,37 +3001,37 @@
         <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G33" t="n">
         <v>0.0003</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="I33" t="n">
         <v>0.05</v>
       </c>
       <c r="J33" t="n">
-        <v>109.5666666666667</v>
+        <v>107.4</v>
       </c>
       <c r="K33" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L33" t="n">
-        <v>13.65462537421776</v>
+        <v>12.81719609944432</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P33" t="n">
         <v>3</v>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.7825858342011425</v>
+        <v>0.7868845130276544</v>
       </c>
       <c r="T33" t="n">
-        <v>0.2391627910236518</v>
+        <v>0.23768160790205</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2390761822462082</v>
+        <v>0.2376122422516346</v>
       </c>
       <c r="V33" t="n">
         <v>30</v>
@@ -3061,7 +3061,7 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kjsd__advperagentrankweighted__M4__L12__eps0p03__g0p0003__ds0p05__dm0p05</t>
+          <t>kjsd__advperagentrankweighted__M4__L12__eps0p03__g0p0003__ds0p2__dm0p05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3087,28 +3087,28 @@
         <v>0.0003</v>
       </c>
       <c r="H34" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="I34" t="n">
         <v>0.05</v>
       </c>
       <c r="J34" t="n">
-        <v>111.6333333333333</v>
+        <v>109.5666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>100.5</v>
+        <v>97</v>
       </c>
       <c r="L34" t="n">
-        <v>13.49492411815598</v>
+        <v>13.65462537421776</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P34" t="n">
         <v>3</v>
@@ -3120,13 +3120,13 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.7784850421281833</v>
+        <v>0.7825858342011425</v>
       </c>
       <c r="T34" t="n">
-        <v>0.2377351808051268</v>
+        <v>0.2391627910236518</v>
       </c>
       <c r="U34" t="n">
-        <v>0.2376587214569251</v>
+        <v>0.2390761822462082</v>
       </c>
       <c r="V34" t="n">
         <v>30</v>
@@ -3138,7 +3138,7 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kjsd__advperagentrankweighted__M4__L10__eps0p03__g0p0003__ds0p2__dm0p05</t>
+          <t>kjsd__advperagentrankweighted__M4__L12__eps0p03__g0p0003__ds0p05__dm0p05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3155,7 +3155,7 @@
         <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F35" t="n">
         <v>0.03</v>
@@ -3164,19 +3164,19 @@
         <v>0.0003</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="I35" t="n">
         <v>0.05</v>
       </c>
       <c r="J35" t="n">
-        <v>127.7333333333333</v>
+        <v>111.6333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>127.5</v>
+        <v>100.5</v>
       </c>
       <c r="L35" t="n">
-        <v>14.34437827283956</v>
+        <v>13.49492411815598</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -3197,13 +3197,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.7465395457940189</v>
+        <v>0.7784850421281833</v>
       </c>
       <c r="T35" t="n">
-        <v>0.2402224982778231</v>
+        <v>0.2377351808051268</v>
       </c>
       <c r="U35" t="n">
-        <v>0.2401511112848918</v>
+        <v>0.2376587214569251</v>
       </c>
       <c r="V35" t="n">
         <v>30</v>
@@ -3215,7 +3215,7 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kjsd__advperagentrankweighted__M4__L10__eps0p03__g0p0003__ds0p05__dm0p05</t>
+          <t>kjsd__advperagentrankweighted__M4__L10__eps0p03__g0p0003__ds0p2__dm0p05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3241,19 +3241,19 @@
         <v>0.0003</v>
       </c>
       <c r="H36" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="I36" t="n">
         <v>0.05</v>
       </c>
       <c r="J36" t="n">
-        <v>135.0333333333333</v>
+        <v>127.7333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>140</v>
+        <v>127.5</v>
       </c>
       <c r="L36" t="n">
-        <v>15.03170241101317</v>
+        <v>14.34437827283956</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -3274,13 +3274,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.732055418809892</v>
+        <v>0.7465395457940189</v>
       </c>
       <c r="T36" t="n">
-        <v>0.2403800442814827</v>
+        <v>0.2402224982778231</v>
       </c>
       <c r="U36" t="n">
-        <v>0.2403172460695108</v>
+        <v>0.2401511112848918</v>
       </c>
       <c r="V36" t="n">
         <v>30</v>
@@ -3292,7 +3292,7 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kjsd__advperagentrankweighted__M4__L8__eps0p03__g0p0003__ds0p2__dm0p05</t>
+          <t>kjsd__advperagentrankweighted__M4__L10__eps0p03__g0p0003__ds0p05__dm0p05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3309,7 +3309,7 @@
         <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F37" t="n">
         <v>0.03</v>
@@ -3318,25 +3318,25 @@
         <v>0.0003</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="I37" t="n">
         <v>0.05</v>
       </c>
       <c r="J37" t="n">
-        <v>160.5</v>
+        <v>135.0333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>176.5</v>
+        <v>140</v>
       </c>
       <c r="L37" t="n">
-        <v>15.44018193771765</v>
+        <v>15.03170241101317</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
@@ -3351,13 +3351,13 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.6815246089599968</v>
+        <v>0.732055418809892</v>
       </c>
       <c r="T37" t="n">
-        <v>0.2398532405495644</v>
+        <v>0.2403800442814827</v>
       </c>
       <c r="U37" t="n">
-        <v>0.2397987099985282</v>
+        <v>0.2403172460695108</v>
       </c>
       <c r="V37" t="n">
         <v>30</v>
@@ -3369,7 +3369,7 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kjsd__advperagentrankweighted__M4__L8__eps0p03__g0p0003__ds0p05__dm0p05</t>
+          <t>kjsd__advperagentrankweighted__M4__L8__eps0p03__g0p0003__ds0p2__dm0p05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3395,55 +3395,131 @@
         <v>0.0003</v>
       </c>
       <c r="H38" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="I38" t="n">
         <v>0.05</v>
       </c>
       <c r="J38" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="L38" t="n">
+        <v>15.44018193771765</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.6815246089599968</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.2398532405495644</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.2397987099985282</v>
+      </c>
+      <c r="V38" t="n">
+        <v>30</v>
+      </c>
+      <c r="W38" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>kjsd__advperagentrankweighted__M4__L8__eps0p03__g0p0003__ds0p05__dm0p05</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>jsd</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>peragentrankweighted</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>8</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J39" t="n">
         <v>163.3</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K39" t="n">
         <v>180.5</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L39" t="n">
         <v>14.70487698316439</v>
       </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
         <v>0.6759668181387865</v>
       </c>
-      <c r="T38" t="n">
+      <c r="T39" t="n">
         <v>0.2410147997240225</v>
       </c>
-      <c r="U38" t="n">
+      <c r="U39" t="n">
         <v>0.2409688790639241</v>
       </c>
-      <c r="V38" t="n">
-        <v>30</v>
-      </c>
-      <c r="W38" t="n">
+      <c r="V39" t="n">
+        <v>30</v>
+      </c>
+      <c r="W39" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1"/>
     <row r="40" ht="18" customHeight="1"/>
     <row r="41" ht="18" customHeight="1"/>
     <row r="42" ht="18" customHeight="1"/>

--- a/results/config/overall_summary.xlsx
+++ b/results/config/overall_summary.xlsx
@@ -2451,7 +2451,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2462,6 +2462,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -2498,16 +2504,16 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -2920,7 +2926,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -2991,7 +2997,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -3062,7 +3068,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1" t="s">
         <v>27</v>
       </c>
@@ -3133,7 +3139,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
@@ -3204,7 +3210,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
@@ -3275,7 +3281,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
@@ -3346,7 +3352,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1" t="s">
         <v>31</v>
       </c>
@@ -3417,7 +3423,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
@@ -3488,7 +3494,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1" t="s">
         <v>33</v>
       </c>
@@ -3559,7 +3565,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
@@ -3630,7 +3636,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
@@ -3701,7 +3707,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -3772,7 +3778,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -3843,7 +3849,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1" t="s">
         <v>38</v>
       </c>
@@ -3914,7 +3920,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
@@ -3985,7 +3991,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="1" t="s">
         <v>40</v>
       </c>
@@ -4056,7 +4062,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
@@ -4127,7 +4133,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -4198,7 +4204,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="1" t="s">
         <v>43</v>
       </c>
@@ -4269,7 +4275,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="1" t="s">
         <v>44</v>
       </c>
@@ -4340,7 +4346,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1" t="s">
         <v>45</v>
       </c>
@@ -4411,7 +4417,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1" t="s">
         <v>46</v>
       </c>
@@ -4482,7 +4488,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
@@ -4553,7 +4559,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="1" t="s">
         <v>48</v>
       </c>
@@ -4624,7 +4630,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="1" t="s">
         <v>49</v>
       </c>
@@ -4695,7 +4701,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="1" t="s">
         <v>50</v>
       </c>
@@ -4766,7 +4772,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="1" t="s">
         <v>51</v>
       </c>
@@ -4837,7 +4843,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="1" t="s">
         <v>52</v>
       </c>
@@ -4908,7 +4914,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="1" t="s">
         <v>53</v>
       </c>
@@ -4979,7 +4985,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="1" t="s">
         <v>54</v>
       </c>
@@ -5050,7 +5056,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="1" t="s">
         <v>55</v>
       </c>
@@ -5121,7 +5127,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="1" t="s">
         <v>56</v>
       </c>
@@ -5192,7 +5198,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="1" t="s">
         <v>57</v>
       </c>
@@ -5263,7 +5269,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="1" t="s">
         <v>58</v>
       </c>
@@ -5334,7 +5340,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="1" t="s">
         <v>59</v>
       </c>
@@ -5405,7 +5411,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="1" t="s">
         <v>60</v>
       </c>
@@ -5476,7 +5482,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="1" t="s">
         <v>61</v>
       </c>
@@ -5547,7 +5553,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="1" t="s">
         <v>62</v>
       </c>
@@ -5618,7 +5624,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="1" t="s">
         <v>63</v>
       </c>
@@ -5689,7 +5695,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="1" t="s">
         <v>64</v>
       </c>
@@ -5760,7 +5766,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="1" t="s">
         <v>65</v>
       </c>
@@ -5831,7 +5837,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="1" t="s">
         <v>66</v>
       </c>
@@ -5902,7 +5908,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="1" t="s">
         <v>67</v>
       </c>
@@ -5973,7 +5979,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="1" t="s">
         <v>68</v>
       </c>
@@ -6044,7 +6050,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="1" t="s">
         <v>69</v>
       </c>
@@ -6115,7 +6121,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="1" t="s">
         <v>70</v>
       </c>
@@ -6186,7 +6192,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="1" t="s">
         <v>71</v>
       </c>
@@ -6257,7 +6263,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="1" t="s">
         <v>72</v>
       </c>
@@ -6328,7 +6334,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="1" t="s">
         <v>73</v>
       </c>
@@ -6399,7 +6405,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="1" t="s">
         <v>74</v>
       </c>
@@ -6470,7 +6476,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,7 +6547,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="1" t="s">
         <v>76</v>
       </c>
